--- a/data/test_ver0.xlsx
+++ b/data/test_ver0.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="5">
   <si>
     <t xml:space="preserve">最大値</t>
   </si>
@@ -36,18 +36,6 @@
   </si>
   <si>
     <t xml:space="preserve">分散</t>
-  </si>
-  <si>
-    <t xml:space="preserve">year</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">B</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C</t>
   </si>
 </sst>
 </file>
@@ -82,9 +70,8 @@
     </font>
     <font>
       <sz val="10"/>
-      <name val="Arial"/>
+      <name val="Noto Sans CJK JP"/>
       <family val="2"/>
-      <charset val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -129,7 +116,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -146,10 +133,6 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -159,7 +142,2065 @@
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="FF000000"/>
+      <rgbColor rgb="FFFFFFFF"/>
+      <rgbColor rgb="FFFF0000"/>
+      <rgbColor rgb="FF00FF00"/>
+      <rgbColor rgb="FF0000FF"/>
+      <rgbColor rgb="FFFFFF00"/>
+      <rgbColor rgb="FFFF00FF"/>
+      <rgbColor rgb="FF00FFFF"/>
+      <rgbColor rgb="FF800000"/>
+      <rgbColor rgb="FF008000"/>
+      <rgbColor rgb="FF000080"/>
+      <rgbColor rgb="FF808000"/>
+      <rgbColor rgb="FF800080"/>
+      <rgbColor rgb="FF008080"/>
+      <rgbColor rgb="FFB3B3B3"/>
+      <rgbColor rgb="FF808080"/>
+      <rgbColor rgb="FF9999FF"/>
+      <rgbColor rgb="FF993366"/>
+      <rgbColor rgb="FFFFFFCC"/>
+      <rgbColor rgb="FFCCFFFF"/>
+      <rgbColor rgb="FF660066"/>
+      <rgbColor rgb="FFFF8080"/>
+      <rgbColor rgb="FF0066CC"/>
+      <rgbColor rgb="FFCCCCFF"/>
+      <rgbColor rgb="FF000080"/>
+      <rgbColor rgb="FFFF00FF"/>
+      <rgbColor rgb="FFFFFF00"/>
+      <rgbColor rgb="FF00FFFF"/>
+      <rgbColor rgb="FF800080"/>
+      <rgbColor rgb="FF800000"/>
+      <rgbColor rgb="FF008080"/>
+      <rgbColor rgb="FF0000FF"/>
+      <rgbColor rgb="FF00CCFF"/>
+      <rgbColor rgb="FFCCFFFF"/>
+      <rgbColor rgb="FFCCFFCC"/>
+      <rgbColor rgb="FFFFFF99"/>
+      <rgbColor rgb="FF99CCFF"/>
+      <rgbColor rgb="FFFF99CC"/>
+      <rgbColor rgb="FFCC99FF"/>
+      <rgbColor rgb="FFFFCC99"/>
+      <rgbColor rgb="FF3366FF"/>
+      <rgbColor rgb="FF33CCCC"/>
+      <rgbColor rgb="FF99CC00"/>
+      <rgbColor rgb="FFFFD320"/>
+      <rgbColor rgb="FFFF9900"/>
+      <rgbColor rgb="FFFF420E"/>
+      <rgbColor rgb="FF666699"/>
+      <rgbColor rgb="FF969696"/>
+      <rgbColor rgb="FF004586"/>
+      <rgbColor rgb="FF339966"/>
+      <rgbColor rgb="FF003300"/>
+      <rgbColor rgb="FF333300"/>
+      <rgbColor rgb="FF993300"/>
+      <rgbColor rgb="FF993366"/>
+      <rgbColor rgb="FF333399"/>
+      <rgbColor rgb="FF333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart34.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <c:chart>
+    <c:autoTitleDeleted val="1"/>
+    <c:plotArea>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$B$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>最大値</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="004586"/>
+            </a:solidFill>
+            <a:ln w="28800">
+              <a:solidFill>
+                <a:srgbClr val="004586"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="square"/>
+            <c:size val="8"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="004586"/>
+              </a:solidFill>
+            </c:spPr>
+          </c:marker>
+          <c:dLbls>
+            <c:txPr>
+              <a:bodyPr wrap="none"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                    <a:latin typeface="Arial"/>
+                  </a:defRPr>
+                </a:pPr>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:separator> </c:separator>
+            <c:showLeaderLines val="1"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet1!$C$2:$G$2</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>4月12日</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>4月13日</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>4月14日</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4月15日</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>4月16日</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$C$3:$G$3</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>600</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>450</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>550</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>650</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>500</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$B$4</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>最小値</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="ff420e"/>
+            </a:solidFill>
+            <a:ln w="28800">
+              <a:solidFill>
+                <a:srgbClr val="ff420e"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="diamond"/>
+            <c:size val="8"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="ff420e"/>
+              </a:solidFill>
+            </c:spPr>
+          </c:marker>
+          <c:dLbls>
+            <c:txPr>
+              <a:bodyPr wrap="none"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                    <a:latin typeface="Arial"/>
+                  </a:defRPr>
+                </a:pPr>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:separator> </c:separator>
+            <c:showLeaderLines val="1"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet1!$C$2:$G$2</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>4月12日</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>4月13日</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>4月14日</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4月15日</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>4月16日</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$C$4:$G$4</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>550</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>500</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>750</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>650</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>450</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$B$5</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>中央値</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="ffd320"/>
+            </a:solidFill>
+            <a:ln w="28800">
+              <a:solidFill>
+                <a:srgbClr val="ffd320"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="triangle"/>
+            <c:size val="8"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="ffd320"/>
+              </a:solidFill>
+            </c:spPr>
+          </c:marker>
+          <c:dLbls>
+            <c:txPr>
+              <a:bodyPr wrap="none"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                    <a:latin typeface="Arial"/>
+                  </a:defRPr>
+                </a:pPr>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:separator> </c:separator>
+            <c:showLeaderLines val="1"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet1!$C$2:$G$2</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>4月12日</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>4月13日</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>4月14日</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4月15日</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>4月16日</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$C$5:$G$5</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>600</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>750</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>600</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>750</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>550</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:hiLowLines>
+          <c:spPr>
+            <a:ln w="0">
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+        </c:hiLowLines>
+        <c:marker val="1"/>
+        <c:axId val="32365636"/>
+        <c:axId val="25223933"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="32365636"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="m\月d\日" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:ln w="0">
+            <a:solidFill>
+              <a:srgbClr val="b3b3b3"/>
+            </a:solidFill>
+          </a:ln>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                <a:latin typeface="Arial"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="25223933"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="25223933"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="0">
+              <a:solidFill>
+                <a:srgbClr val="b3b3b3"/>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:ln w="0">
+            <a:solidFill>
+              <a:srgbClr val="b3b3b3"/>
+            </a:solidFill>
+          </a:ln>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                <a:latin typeface="Arial"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="32365636"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:solidFill>
+            <a:srgbClr val="b3b3b3"/>
+          </a:solidFill>
+        </a:ln>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+              <a:latin typeface="Arial"/>
+            </a:defRPr>
+          </a:pPr>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:srgbClr val="ffffff"/>
+    </a:solidFill>
+    <a:ln w="0">
+      <a:noFill/>
+    </a:ln>
+  </c:spPr>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart35.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <c:chart>
+    <c:autoTitleDeleted val="1"/>
+    <c:plotArea>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$B$17</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>標準偏差</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="004586"/>
+            </a:solidFill>
+            <a:ln w="28800">
+              <a:solidFill>
+                <a:srgbClr val="004586"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="square"/>
+            <c:size val="8"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="004586"/>
+              </a:solidFill>
+            </c:spPr>
+          </c:marker>
+          <c:dLbls>
+            <c:txPr>
+              <a:bodyPr wrap="none"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                    <a:latin typeface="Arial"/>
+                  </a:defRPr>
+                </a:pPr>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:separator> </c:separator>
+            <c:showLeaderLines val="1"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet1!$C$16:$G$16</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>4月12日</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>4月13日</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>4月14日</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4月15日</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>4月16日</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$C$17:$G$17</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>450</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>650</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>600</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>450</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>500</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$B$18</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>中央値</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="ff420e"/>
+            </a:solidFill>
+            <a:ln w="28800">
+              <a:solidFill>
+                <a:srgbClr val="ff420e"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="diamond"/>
+            <c:size val="8"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="ff420e"/>
+              </a:solidFill>
+            </c:spPr>
+          </c:marker>
+          <c:dLbls>
+            <c:txPr>
+              <a:bodyPr wrap="none"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                    <a:latin typeface="Arial"/>
+                  </a:defRPr>
+                </a:pPr>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:separator> </c:separator>
+            <c:showLeaderLines val="1"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet1!$C$16:$G$16</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>4月12日</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>4月13日</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>4月14日</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4月15日</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>4月16日</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$C$18:$G$18</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>450</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>550</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>650</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>500</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>450</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$B$19</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>分散</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="ffd320"/>
+            </a:solidFill>
+            <a:ln w="28800">
+              <a:solidFill>
+                <a:srgbClr val="ffd320"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="triangle"/>
+            <c:size val="8"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="ffd320"/>
+              </a:solidFill>
+            </c:spPr>
+          </c:marker>
+          <c:dLbls>
+            <c:txPr>
+              <a:bodyPr wrap="none"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                    <a:latin typeface="Arial"/>
+                  </a:defRPr>
+                </a:pPr>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:separator> </c:separator>
+            <c:showLeaderLines val="1"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet1!$C$16:$G$16</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>4月12日</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>4月13日</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>4月14日</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4月15日</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>4月16日</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$C$19:$G$19</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>500</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>750</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>650</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>450</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>550</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:hiLowLines>
+          <c:spPr>
+            <a:ln w="0">
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+        </c:hiLowLines>
+        <c:marker val="1"/>
+        <c:axId val="94619446"/>
+        <c:axId val="2293373"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="94619446"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="m\月d\日" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:ln w="0">
+            <a:solidFill>
+              <a:srgbClr val="b3b3b3"/>
+            </a:solidFill>
+          </a:ln>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                <a:latin typeface="Arial"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="2293373"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="2293373"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="0">
+              <a:solidFill>
+                <a:srgbClr val="b3b3b3"/>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:ln w="0">
+            <a:solidFill>
+              <a:srgbClr val="b3b3b3"/>
+            </a:solidFill>
+          </a:ln>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                <a:latin typeface="Arial"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="94619446"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:solidFill>
+            <a:srgbClr val="b3b3b3"/>
+          </a:solidFill>
+        </a:ln>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+              <a:latin typeface="Arial"/>
+            </a:defRPr>
+          </a:pPr>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:srgbClr val="ffffff"/>
+    </a:solidFill>
+    <a:ln w="0">
+      <a:noFill/>
+    </a:ln>
+  </c:spPr>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart36.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <c:chart>
+    <c:autoTitleDeleted val="1"/>
+    <c:plotArea>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet2!$B$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>最大値</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="004586"/>
+            </a:solidFill>
+            <a:ln w="28800">
+              <a:solidFill>
+                <a:srgbClr val="004586"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="square"/>
+            <c:size val="8"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="004586"/>
+              </a:solidFill>
+            </c:spPr>
+          </c:marker>
+          <c:dLbls>
+            <c:txPr>
+              <a:bodyPr wrap="none"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                    <a:latin typeface="Arial"/>
+                  </a:defRPr>
+                </a:pPr>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:separator> </c:separator>
+            <c:showLeaderLines val="1"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet2!$C$2:$G$2</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>4月17日</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>4月18日</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>4月19日</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4月20日</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>4月21日</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet2!$C$3:$G$3</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>450</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>450</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>650</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>450</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>450</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet2!$B$4</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>最小値</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="ff420e"/>
+            </a:solidFill>
+            <a:ln w="28800">
+              <a:solidFill>
+                <a:srgbClr val="ff420e"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="diamond"/>
+            <c:size val="8"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="ff420e"/>
+              </a:solidFill>
+            </c:spPr>
+          </c:marker>
+          <c:dLbls>
+            <c:txPr>
+              <a:bodyPr wrap="none"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                    <a:latin typeface="Arial"/>
+                  </a:defRPr>
+                </a:pPr>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:separator> </c:separator>
+            <c:showLeaderLines val="1"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet2!$C$2:$G$2</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>4月17日</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>4月18日</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>4月19日</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4月20日</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>4月21日</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet2!$C$4:$G$4</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>500</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>500</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>550</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>500</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>450</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet2!$B$5</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>中央値</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="ffd320"/>
+            </a:solidFill>
+            <a:ln w="28800">
+              <a:solidFill>
+                <a:srgbClr val="ffd320"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="triangle"/>
+            <c:size val="8"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="ffd320"/>
+              </a:solidFill>
+            </c:spPr>
+          </c:marker>
+          <c:dLbls>
+            <c:txPr>
+              <a:bodyPr wrap="none"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                    <a:latin typeface="Arial"/>
+                  </a:defRPr>
+                </a:pPr>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:separator> </c:separator>
+            <c:showLeaderLines val="1"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet2!$C$2:$G$2</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>4月17日</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>4月18日</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>4月19日</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4月20日</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>4月21日</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet2!$C$5:$G$5</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>450</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>450</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>750</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>450</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>450</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:hiLowLines>
+          <c:spPr>
+            <a:ln w="0">
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+        </c:hiLowLines>
+        <c:marker val="1"/>
+        <c:axId val="80543048"/>
+        <c:axId val="16874077"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="80543048"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="m\月d\日" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:ln w="0">
+            <a:solidFill>
+              <a:srgbClr val="b3b3b3"/>
+            </a:solidFill>
+          </a:ln>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                <a:latin typeface="Arial"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="16874077"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="16874077"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="0">
+              <a:solidFill>
+                <a:srgbClr val="b3b3b3"/>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:ln w="0">
+            <a:solidFill>
+              <a:srgbClr val="b3b3b3"/>
+            </a:solidFill>
+          </a:ln>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                <a:latin typeface="Arial"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="80543048"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:solidFill>
+            <a:srgbClr val="b3b3b3"/>
+          </a:solidFill>
+        </a:ln>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+              <a:latin typeface="Arial"/>
+            </a:defRPr>
+          </a:pPr>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:srgbClr val="ffffff"/>
+    </a:solidFill>
+    <a:ln w="0">
+      <a:noFill/>
+    </a:ln>
+  </c:spPr>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart37.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <c:chart>
+    <c:autoTitleDeleted val="1"/>
+    <c:plotArea>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet2!$B$17</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>標準偏差</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="004586"/>
+            </a:solidFill>
+            <a:ln w="28800">
+              <a:solidFill>
+                <a:srgbClr val="004586"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="square"/>
+            <c:size val="8"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="004586"/>
+              </a:solidFill>
+            </c:spPr>
+          </c:marker>
+          <c:dLbls>
+            <c:txPr>
+              <a:bodyPr wrap="none"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                    <a:latin typeface="Arial"/>
+                  </a:defRPr>
+                </a:pPr>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:separator> </c:separator>
+            <c:showLeaderLines val="1"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet2!$C$16:$G$16</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>4月17日</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>4月18日</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>4月19日</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4月20日</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>4月21日</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet2!$C$17:$G$17</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>450</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>650</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>450</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>650</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>500</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet2!$B$18</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>中央値</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="ff420e"/>
+            </a:solidFill>
+            <a:ln w="28800">
+              <a:solidFill>
+                <a:srgbClr val="ff420e"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="diamond"/>
+            <c:size val="8"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="ff420e"/>
+              </a:solidFill>
+            </c:spPr>
+          </c:marker>
+          <c:dLbls>
+            <c:txPr>
+              <a:bodyPr wrap="none"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                    <a:latin typeface="Arial"/>
+                  </a:defRPr>
+                </a:pPr>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:separator> </c:separator>
+            <c:showLeaderLines val="1"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet2!$C$16:$G$16</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>4月17日</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>4月18日</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>4月19日</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4月20日</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>4月21日</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet2!$C$18:$G$18</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>450</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>550</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>500</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>550</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>450</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet2!$B$19</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>分散</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="ffd320"/>
+            </a:solidFill>
+            <a:ln w="28800">
+              <a:solidFill>
+                <a:srgbClr val="ffd320"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="triangle"/>
+            <c:size val="8"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="ffd320"/>
+              </a:solidFill>
+            </c:spPr>
+          </c:marker>
+          <c:dLbls>
+            <c:txPr>
+              <a:bodyPr wrap="none"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                    <a:latin typeface="Arial"/>
+                  </a:defRPr>
+                </a:pPr>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:separator> </c:separator>
+            <c:showLeaderLines val="1"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet2!$C$16:$G$16</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>4月17日</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>4月18日</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>4月19日</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4月20日</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>4月21日</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet2!$C$19:$G$19</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>500</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>750</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>450</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>750</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>550</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:hiLowLines>
+          <c:spPr>
+            <a:ln w="0">
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+        </c:hiLowLines>
+        <c:marker val="1"/>
+        <c:axId val="54400891"/>
+        <c:axId val="72015862"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="54400891"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="m\月d\日" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:ln w="0">
+            <a:solidFill>
+              <a:srgbClr val="b3b3b3"/>
+            </a:solidFill>
+          </a:ln>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                <a:latin typeface="Arial"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="72015862"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="72015862"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="0">
+              <a:solidFill>
+                <a:srgbClr val="b3b3b3"/>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:ln w="0">
+            <a:solidFill>
+              <a:srgbClr val="b3b3b3"/>
+            </a:solidFill>
+          </a:ln>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                <a:latin typeface="Arial"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="54400891"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:solidFill>
+            <a:srgbClr val="b3b3b3"/>
+          </a:solidFill>
+        </a:ln>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+              <a:latin typeface="Arial"/>
+            </a:defRPr>
+          </a:pPr>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:srgbClr val="ffffff"/>
+    </a:solidFill>
+    <a:ln w="0">
+      <a:noFill/>
+    </a:ln>
+  </c:spPr>
+</c:chartSpace>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>49320</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>57600</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>632520</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>127080</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame>
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="0" name=""/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="11535120" y="57600"/>
+        <a:ext cx="3864960" cy="2219040"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>29520</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>146880</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>701640</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>131400</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame>
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="1" name=""/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="11515320" y="2458800"/>
+        <a:ext cx="3953880" cy="2459160"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>31680</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>584640</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>57600</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame>
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name=""/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="11485800" y="31680"/>
+        <a:ext cx="3866400" cy="2175480"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>29520</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>74520</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>675720</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>134280</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame>
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name=""/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="11515320" y="2549160"/>
+        <a:ext cx="3927960" cy="2209320"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -168,7 +2209,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A2:G19"/>
-  <sheetFormatPr defaultColWidth="11.625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.640625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="2" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C2" s="1" t="n">
@@ -347,6 +2388,7 @@
     <oddHeader>&amp;C&amp;"Times New Roman,標準"&amp;12&amp;A</oddHeader>
     <oddFooter>&amp;C&amp;"Times New Roman,標準"&amp;12ページ &amp;P</oddFooter>
   </headerFooter>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -355,171 +2397,175 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:G32"/>
-  <sheetFormatPr defaultColWidth="11.58984375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A2:G19"/>
+  <sheetFormatPr defaultColWidth="11.640625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
-    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="B1" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="D1" s="4" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="n">
-        <v>2017</v>
-      </c>
-      <c r="B2" s="2" t="n">
-        <v>600</v>
-      </c>
-      <c r="C2" s="2" t="n">
-        <v>450</v>
-      </c>
-      <c r="D2" s="2" t="n">
-        <v>400</v>
+    <row r="2" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C2" s="1" t="n">
+        <v>45033</v>
+      </c>
+      <c r="D2" s="1" t="n">
+        <f aca="false">C2+1</f>
+        <v>45034</v>
+      </c>
+      <c r="E2" s="1" t="n">
+        <f aca="false">D2+1</f>
+        <v>45035</v>
+      </c>
+      <c r="F2" s="1" t="n">
+        <f aca="false">E2+1</f>
+        <v>45036</v>
+      </c>
+      <c r="G2" s="1" t="n">
+        <f aca="false">F2+1</f>
+        <v>45037</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="2" t="n">
-        <v>2018</v>
-      </c>
-      <c r="B3" s="2" t="n">
-        <v>550</v>
-      </c>
-      <c r="C3" s="2" t="n">
-        <v>500</v>
-      </c>
-      <c r="D3" s="2" t="n">
-        <v>350</v>
+      <c r="B3" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>450</v>
+      </c>
+      <c r="D3" s="3" t="n">
+        <v>450</v>
+      </c>
+      <c r="E3" s="3" t="n">
+        <v>650</v>
+      </c>
+      <c r="F3" s="3" t="n">
+        <v>450</v>
+      </c>
+      <c r="G3" s="3" t="n">
+        <v>450</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="2" t="n">
-        <v>2019</v>
-      </c>
-      <c r="B4" s="2" t="n">
-        <v>750</v>
-      </c>
-      <c r="C4" s="2" t="n">
-        <v>650</v>
-      </c>
-      <c r="D4" s="2" t="n">
+      <c r="B4" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>500</v>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v>500</v>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>550</v>
+      </c>
+      <c r="F4" s="3" t="n">
+        <v>500</v>
+      </c>
+      <c r="G4" s="3" t="n">
         <v>450</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="2" t="n">
-        <v>2020</v>
-      </c>
-      <c r="B5" s="2" t="n">
-        <v>600</v>
-      </c>
-      <c r="C5" s="2" t="n">
+      <c r="A5" s="2"/>
+      <c r="B5" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>450</v>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>450</v>
+      </c>
+      <c r="E5" s="3" t="n">
         <v>750</v>
       </c>
-      <c r="D5" s="2" t="n">
-        <v>550</v>
+      <c r="F5" s="3" t="n">
+        <v>450</v>
+      </c>
+      <c r="G5" s="3" t="n">
+        <v>450</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="2" t="n">
-        <v>2021</v>
-      </c>
-      <c r="B6" s="2" t="n">
-        <v>800</v>
-      </c>
-      <c r="C6" s="2" t="n">
+      <c r="A6" s="2"/>
+      <c r="B6" s="2"/>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
+    </row>
+    <row r="16" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C16" s="1" t="n">
+        <v>45033</v>
+      </c>
+      <c r="D16" s="1" t="n">
+        <f aca="false">C16+1</f>
+        <v>45034</v>
+      </c>
+      <c r="E16" s="1" t="n">
+        <f aca="false">D16+1</f>
+        <v>45035</v>
+      </c>
+      <c r="F16" s="1" t="n">
+        <f aca="false">E16+1</f>
+        <v>45036</v>
+      </c>
+      <c r="G16" s="1" t="n">
+        <f aca="false">F16+1</f>
+        <v>45037</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B17" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C17" s="3" t="n">
+        <v>450</v>
+      </c>
+      <c r="D17" s="3" t="n">
         <v>650</v>
       </c>
-      <c r="D6" s="2" t="n">
+      <c r="E17" s="3" t="n">
+        <v>450</v>
+      </c>
+      <c r="F17" s="3" t="n">
+        <v>650</v>
+      </c>
+      <c r="G17" s="3" t="n">
         <v>500</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C29" s="1" t="n">
-        <v>45028</v>
-      </c>
-      <c r="D29" s="1" t="n">
-        <f aca="false">C29+1</f>
-        <v>45029</v>
-      </c>
-      <c r="E29" s="1" t="n">
-        <f aca="false">D29+1</f>
-        <v>45030</v>
-      </c>
-      <c r="F29" s="1" t="n">
-        <f aca="false">E29+1</f>
-        <v>45031</v>
-      </c>
-      <c r="G29" s="1" t="n">
-        <f aca="false">F29+1</f>
-        <v>45032</v>
+    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B18" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C18" s="3" t="n">
+        <v>450</v>
+      </c>
+      <c r="D18" s="3" t="n">
+        <v>550</v>
+      </c>
+      <c r="E18" s="3" t="n">
+        <v>500</v>
+      </c>
+      <c r="F18" s="3" t="n">
+        <v>550</v>
+      </c>
+      <c r="G18" s="3" t="n">
+        <v>450</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B30" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="C30" s="3" t="n">
-        <v>600</v>
-      </c>
-      <c r="D30" s="3" t="n">
+    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B19" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C19" s="3" t="n">
+        <v>500</v>
+      </c>
+      <c r="D19" s="3" t="n">
+        <v>750</v>
+      </c>
+      <c r="E19" s="3" t="n">
         <v>450</v>
       </c>
-      <c r="E30" s="3" t="n">
-        <v>550</v>
-      </c>
-      <c r="F30" s="3" t="n">
-        <v>650</v>
-      </c>
-      <c r="G30" s="3" t="n">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B31" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C31" s="3" t="n">
-        <v>550</v>
-      </c>
-      <c r="D31" s="3" t="n">
-        <v>500</v>
-      </c>
-      <c r="E31" s="3" t="n">
+      <c r="F19" s="3" t="n">
         <v>750</v>
       </c>
-      <c r="F31" s="3" t="n">
-        <v>650</v>
-      </c>
-      <c r="G31" s="3" t="n">
-        <v>450</v>
-      </c>
-    </row>
-    <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B32" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="C32" s="3" t="n">
-        <v>600</v>
-      </c>
-      <c r="D32" s="3" t="n">
-        <v>750</v>
-      </c>
-      <c r="E32" s="3" t="n">
-        <v>600</v>
-      </c>
-      <c r="F32" s="3" t="n">
-        <v>750</v>
-      </c>
-      <c r="G32" s="3" t="n">
+      <c r="G19" s="3" t="n">
         <v>550</v>
       </c>
     </row>
@@ -531,5 +2577,6 @@
     <oddHeader>&amp;C&amp;"Times New Roman,標準"&amp;12&amp;A</oddHeader>
     <oddFooter>&amp;C&amp;"Times New Roman,標準"&amp;12ページ &amp;P</oddFooter>
   </headerFooter>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/data/test_ver0.xlsx
+++ b/data/test_ver0.xlsx
@@ -5,11 +5,12 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId2"/>
     <sheet name="Sheet2" sheetId="2" state="visible" r:id="rId3"/>
+    <sheet name="Sheet3" sheetId="3" state="visible" r:id="rId4"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
@@ -21,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="5">
   <si>
     <t xml:space="preserve">最大値</t>
   </si>
@@ -46,7 +47,7 @@
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="m\月d\日"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <sz val="10"/>
       <name val="Noto Sans CJK JP"/>
@@ -70,6 +71,12 @@
     </font>
     <font>
       <sz val="10"/>
+      <name val="Noto Sans CJK JP"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
       <name val="Noto Sans CJK JP"/>
       <family val="2"/>
     </font>
@@ -116,7 +123,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -130,6 +137,14 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -159,15 +174,15 @@
       <rgbColor rgb="FF800080"/>
       <rgbColor rgb="FF008080"/>
       <rgbColor rgb="FFB3B3B3"/>
-      <rgbColor rgb="FF808080"/>
+      <rgbColor rgb="FF878787"/>
       <rgbColor rgb="FF9999FF"/>
-      <rgbColor rgb="FF993366"/>
+      <rgbColor rgb="FFBE4B48"/>
       <rgbColor rgb="FFFFFFCC"/>
       <rgbColor rgb="FFCCFFFF"/>
       <rgbColor rgb="FF660066"/>
       <rgbColor rgb="FFFF8080"/>
       <rgbColor rgb="FF0066CC"/>
-      <rgbColor rgb="FFCCCCFF"/>
+      <rgbColor rgb="FFD9D9D9"/>
       <rgbColor rgb="FF000080"/>
       <rgbColor rgb="FFFF00FF"/>
       <rgbColor rgb="FFFFFF00"/>
@@ -186,11 +201,11 @@
       <rgbColor rgb="FFFFCC99"/>
       <rgbColor rgb="FF3366FF"/>
       <rgbColor rgb="FF33CCCC"/>
-      <rgbColor rgb="FF99CC00"/>
+      <rgbColor rgb="FF98B855"/>
       <rgbColor rgb="FFFFD320"/>
       <rgbColor rgb="FFFF9900"/>
       <rgbColor rgb="FFFF420E"/>
-      <rgbColor rgb="FF666699"/>
+      <rgbColor rgb="FF4A7EBB"/>
       <rgbColor rgb="FF969696"/>
       <rgbColor rgb="FF004586"/>
       <rgbColor rgb="FF339966"/>
@@ -205,7 +220,7 @@
 </styleSheet>
 </file>
 
-<file path=xl/charts/chart34.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart61.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
@@ -261,6 +276,7 @@
                 </a:pPr>
               </a:p>
             </c:txPr>
+            <c:dLblPos val="r"/>
             <c:showLegendKey val="0"/>
             <c:showVal val="0"/>
             <c:showCatName val="0"/>
@@ -369,6 +385,7 @@
                 </a:pPr>
               </a:p>
             </c:txPr>
+            <c:dLblPos val="r"/>
             <c:showLegendKey val="0"/>
             <c:showVal val="0"/>
             <c:showCatName val="0"/>
@@ -477,6 +494,7 @@
                 </a:pPr>
               </a:p>
             </c:txPr>
+            <c:dLblPos val="r"/>
             <c:showLegendKey val="0"/>
             <c:showVal val="0"/>
             <c:showCatName val="0"/>
@@ -547,17 +565,17 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="1"/>
-        <c:axId val="32365636"/>
-        <c:axId val="25223933"/>
+        <c:axId val="90418903"/>
+        <c:axId val="72546388"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="32365636"/>
+        <c:axId val="90418903"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="b"/>
-        <c:numFmt formatCode="m\月d\日" sourceLinked="1"/>
+        <c:numFmt formatCode="m\月d\日" sourceLinked="0"/>
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -579,7 +597,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="25223933"/>
+        <c:crossAx val="72546388"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -587,7 +605,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="25223933"/>
+        <c:axId val="72546388"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -602,7 +620,7 @@
             </a:ln>
           </c:spPr>
         </c:majorGridlines>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:numFmt formatCode="General" sourceLinked="0"/>
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -624,7 +642,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="32365636"/>
+        <c:crossAx val="90418903"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -672,7 +690,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart35.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart62.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
@@ -728,6 +746,7 @@
                 </a:pPr>
               </a:p>
             </c:txPr>
+            <c:dLblPos val="r"/>
             <c:showLegendKey val="0"/>
             <c:showVal val="0"/>
             <c:showCatName val="0"/>
@@ -836,6 +855,7 @@
                 </a:pPr>
               </a:p>
             </c:txPr>
+            <c:dLblPos val="r"/>
             <c:showLegendKey val="0"/>
             <c:showVal val="0"/>
             <c:showCatName val="0"/>
@@ -944,6 +964,7 @@
                 </a:pPr>
               </a:p>
             </c:txPr>
+            <c:dLblPos val="r"/>
             <c:showLegendKey val="0"/>
             <c:showVal val="0"/>
             <c:showCatName val="0"/>
@@ -1014,17 +1035,17 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="1"/>
-        <c:axId val="94619446"/>
-        <c:axId val="2293373"/>
+        <c:axId val="56819479"/>
+        <c:axId val="58805529"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="94619446"/>
+        <c:axId val="56819479"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="b"/>
-        <c:numFmt formatCode="m\月d\日" sourceLinked="1"/>
+        <c:numFmt formatCode="m\月d\日" sourceLinked="0"/>
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -1046,7 +1067,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="2293373"/>
+        <c:crossAx val="58805529"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1054,7 +1075,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="2293373"/>
+        <c:axId val="58805529"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1069,7 +1090,7 @@
             </a:ln>
           </c:spPr>
         </c:majorGridlines>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:numFmt formatCode="General" sourceLinked="0"/>
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -1091,7 +1112,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="94619446"/>
+        <c:crossAx val="56819479"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -1139,7 +1160,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart36.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart63.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
@@ -1195,6 +1216,7 @@
                 </a:pPr>
               </a:p>
             </c:txPr>
+            <c:dLblPos val="r"/>
             <c:showLegendKey val="0"/>
             <c:showVal val="0"/>
             <c:showCatName val="0"/>
@@ -1303,6 +1325,7 @@
                 </a:pPr>
               </a:p>
             </c:txPr>
+            <c:dLblPos val="r"/>
             <c:showLegendKey val="0"/>
             <c:showVal val="0"/>
             <c:showCatName val="0"/>
@@ -1411,6 +1434,7 @@
                 </a:pPr>
               </a:p>
             </c:txPr>
+            <c:dLblPos val="r"/>
             <c:showLegendKey val="0"/>
             <c:showVal val="0"/>
             <c:showCatName val="0"/>
@@ -1481,17 +1505,17 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="1"/>
-        <c:axId val="80543048"/>
-        <c:axId val="16874077"/>
+        <c:axId val="1602152"/>
+        <c:axId val="30615020"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="80543048"/>
+        <c:axId val="1602152"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="b"/>
-        <c:numFmt formatCode="m\月d\日" sourceLinked="1"/>
+        <c:numFmt formatCode="m\月d\日" sourceLinked="0"/>
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -1513,7 +1537,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="16874077"/>
+        <c:crossAx val="30615020"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1521,7 +1545,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="16874077"/>
+        <c:axId val="30615020"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1536,7 +1560,7 @@
             </a:ln>
           </c:spPr>
         </c:majorGridlines>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:numFmt formatCode="General" sourceLinked="0"/>
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -1558,7 +1582,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="80543048"/>
+        <c:crossAx val="1602152"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -1606,7 +1630,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart37.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart64.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
@@ -1662,6 +1686,7 @@
                 </a:pPr>
               </a:p>
             </c:txPr>
+            <c:dLblPos val="r"/>
             <c:showLegendKey val="0"/>
             <c:showVal val="0"/>
             <c:showCatName val="0"/>
@@ -1770,6 +1795,7 @@
                 </a:pPr>
               </a:p>
             </c:txPr>
+            <c:dLblPos val="r"/>
             <c:showLegendKey val="0"/>
             <c:showVal val="0"/>
             <c:showCatName val="0"/>
@@ -1878,6 +1904,7 @@
                 </a:pPr>
               </a:p>
             </c:txPr>
+            <c:dLblPos val="r"/>
             <c:showLegendKey val="0"/>
             <c:showVal val="0"/>
             <c:showCatName val="0"/>
@@ -1948,17 +1975,17 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="1"/>
-        <c:axId val="54400891"/>
-        <c:axId val="72015862"/>
+        <c:axId val="36264543"/>
+        <c:axId val="41032362"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="54400891"/>
+        <c:axId val="36264543"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="b"/>
-        <c:numFmt formatCode="m\月d\日" sourceLinked="1"/>
+        <c:numFmt formatCode="m\月d\日" sourceLinked="0"/>
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -1980,7 +2007,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="72015862"/>
+        <c:crossAx val="41032362"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1988,7 +2015,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="72015862"/>
+        <c:axId val="41032362"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2003,7 +2030,7 @@
             </a:ln>
           </c:spPr>
         </c:majorGridlines>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:numFmt formatCode="General" sourceLinked="0"/>
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -2025,7 +2052,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="54400891"/>
+        <c:crossAx val="36264543"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -2073,6 +2100,4938 @@
 </c:chartSpace>
 </file>
 
+<file path=xl/charts/chart65.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <c:chart>
+    <c:autoTitleDeleted val="1"/>
+    <c:plotArea>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet3!$B$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>最大値</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="004586"/>
+            </a:solidFill>
+            <a:ln w="28800">
+              <a:solidFill>
+                <a:srgbClr val="004586"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="square"/>
+            <c:size val="8"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="004586"/>
+              </a:solidFill>
+            </c:spPr>
+          </c:marker>
+          <c:dLbls>
+            <c:txPr>
+              <a:bodyPr wrap="square"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="Arial"/>
+                  </a:defRPr>
+                </a:pPr>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="r"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:separator>; </c:separator>
+            <c:showLeaderLines val="1"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet3!$C$2:$G$2</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>4月22日</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>4月23日</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>4月24日</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4月25日</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>4月26日</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet3!$C$3:$G$3</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>650</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>650</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>650</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>450</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>450</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet3!$B$4</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>最小値</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="ff420e"/>
+            </a:solidFill>
+            <a:ln w="28800">
+              <a:solidFill>
+                <a:srgbClr val="ff420e"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="diamond"/>
+            <c:size val="8"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="ff420e"/>
+              </a:solidFill>
+            </c:spPr>
+          </c:marker>
+          <c:dLbls>
+            <c:txPr>
+              <a:bodyPr wrap="square"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="Arial"/>
+                  </a:defRPr>
+                </a:pPr>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="r"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:separator>; </c:separator>
+            <c:showLeaderLines val="1"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet3!$C$2:$G$2</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>4月22日</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>4月23日</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>4月24日</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4月25日</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>4月26日</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet3!$C$4:$G$4</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>550</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>550</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>550</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>500</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>450</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet3!$B$5</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>中央値</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="ffd320"/>
+            </a:solidFill>
+            <a:ln w="28800">
+              <a:solidFill>
+                <a:srgbClr val="ffd320"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="triangle"/>
+            <c:size val="8"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="ffd320"/>
+              </a:solidFill>
+            </c:spPr>
+          </c:marker>
+          <c:dLbls>
+            <c:txPr>
+              <a:bodyPr wrap="square"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="Arial"/>
+                  </a:defRPr>
+                </a:pPr>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="r"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:separator>; </c:separator>
+            <c:showLeaderLines val="1"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet3!$C$2:$G$2</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>4月22日</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>4月23日</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>4月24日</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4月25日</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>4月26日</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet3!$C$5:$G$5</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>650</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>650</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>750</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>450</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>450</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:hiLowLines>
+          <c:spPr>
+            <a:ln w="0">
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+        </c:hiLowLines>
+        <c:marker val="1"/>
+        <c:axId val="62269612"/>
+        <c:axId val="80680574"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="62269612"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="m\月d\日" sourceLinked="0"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:ln w="0">
+            <a:solidFill>
+              <a:srgbClr val="b3b3b3"/>
+            </a:solidFill>
+          </a:ln>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="Arial"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="80680574"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="80680574"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="0">
+              <a:solidFill>
+                <a:srgbClr val="b3b3b3"/>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="0"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:ln w="0">
+            <a:solidFill>
+              <a:srgbClr val="b3b3b3"/>
+            </a:solidFill>
+          </a:ln>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="Arial"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="62269612"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Arial"/>
+            </a:defRPr>
+          </a:pPr>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:srgbClr val="ffffff"/>
+    </a:solidFill>
+    <a:ln w="0">
+      <a:noFill/>
+    </a:ln>
+  </c:spPr>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart66.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <c:chart>
+    <c:autoTitleDeleted val="1"/>
+    <c:plotArea>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet3!$B$17</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>標準偏差</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="004586"/>
+            </a:solidFill>
+            <a:ln w="28800">
+              <a:solidFill>
+                <a:srgbClr val="004586"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="square"/>
+            <c:size val="8"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="004586"/>
+              </a:solidFill>
+            </c:spPr>
+          </c:marker>
+          <c:dLbls>
+            <c:txPr>
+              <a:bodyPr wrap="square"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="Arial"/>
+                  </a:defRPr>
+                </a:pPr>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="r"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:separator>; </c:separator>
+            <c:showLeaderLines val="1"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet3!$C$16:$G$16</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>4月22日</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>4月23日</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>4月24日</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4月25日</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>4月26日</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet3!$C$17:$G$17</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>650</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>650</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>450</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>650</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>500</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet3!$B$18</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>中央値</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="ff420e"/>
+            </a:solidFill>
+            <a:ln w="28800">
+              <a:solidFill>
+                <a:srgbClr val="ff420e"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="diamond"/>
+            <c:size val="8"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="ff420e"/>
+              </a:solidFill>
+            </c:spPr>
+          </c:marker>
+          <c:dLbls>
+            <c:txPr>
+              <a:bodyPr wrap="square"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="Arial"/>
+                  </a:defRPr>
+                </a:pPr>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="r"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:separator>; </c:separator>
+            <c:showLeaderLines val="1"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet3!$C$16:$G$16</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>4月22日</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>4月23日</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>4月24日</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4月25日</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>4月26日</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet3!$C$18:$G$18</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>550</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>550</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>500</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>550</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>450</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet3!$B$19</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>分散</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="ffd320"/>
+            </a:solidFill>
+            <a:ln w="28800">
+              <a:solidFill>
+                <a:srgbClr val="ffd320"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="triangle"/>
+            <c:size val="8"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="ffd320"/>
+              </a:solidFill>
+            </c:spPr>
+          </c:marker>
+          <c:dLbls>
+            <c:txPr>
+              <a:bodyPr wrap="square"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="Arial"/>
+                  </a:defRPr>
+                </a:pPr>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="r"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:separator>; </c:separator>
+            <c:showLeaderLines val="1"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet3!$C$16:$G$16</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>4月22日</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>4月23日</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>4月24日</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4月25日</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>4月26日</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet3!$C$19:$G$19</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>750</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>750</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>450</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>750</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>550</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:hiLowLines>
+          <c:spPr>
+            <a:ln w="0">
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+        </c:hiLowLines>
+        <c:marker val="1"/>
+        <c:axId val="78939688"/>
+        <c:axId val="70507271"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="78939688"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="m\月d\日" sourceLinked="0"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:ln w="0">
+            <a:solidFill>
+              <a:srgbClr val="b3b3b3"/>
+            </a:solidFill>
+          </a:ln>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="Arial"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="70507271"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="70507271"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="0">
+              <a:solidFill>
+                <a:srgbClr val="b3b3b3"/>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="0"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:ln w="0">
+            <a:solidFill>
+              <a:srgbClr val="b3b3b3"/>
+            </a:solidFill>
+          </a:ln>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="Arial"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="78939688"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Arial"/>
+            </a:defRPr>
+          </a:pPr>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:srgbClr val="ffffff"/>
+    </a:solidFill>
+    <a:ln w="0">
+      <a:noFill/>
+    </a:ln>
+  </c:spPr>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart67.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <c:chart>
+    <c:autoTitleDeleted val="1"/>
+    <c:plotArea>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>"最大値"</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>最大値</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="4a7ebb"/>
+            </a:solidFill>
+            <a:ln w="28440">
+              <a:solidFill>
+                <a:srgbClr val="4a7ebb"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:dLbls>
+            <c:txPr>
+              <a:bodyPr wrap="square"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="Arial"/>
+                  </a:defRPr>
+                </a:pPr>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="r"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:separator>; </c:separator>
+            <c:showLeaderLines val="1"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:multiLvlStrRef>
+              <c:f>Sheet2!$C$2:$G$2</c:f>
+              <c:multiLvlStrCache>
+                <c:ptCount val="1"/>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>4月21日</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>4月20日</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>4月19日</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>4月18日</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>4月17日</c:v>
+                  </c:pt>
+                </c:lvl>
+              </c:multiLvlStrCache>
+            </c:multiLvlStrRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet2!$C$3:$G$3</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>450</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>450</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>650</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>450</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>450</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>"最小値"</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>最小値</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="be4b48"/>
+            </a:solidFill>
+            <a:ln w="28440">
+              <a:solidFill>
+                <a:srgbClr val="be4b48"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:dLbls>
+            <c:txPr>
+              <a:bodyPr wrap="square"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="Arial"/>
+                  </a:defRPr>
+                </a:pPr>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="r"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:separator>; </c:separator>
+            <c:showLeaderLines val="1"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:multiLvlStrRef>
+              <c:f>Sheet2!$C$2:$G$2</c:f>
+              <c:multiLvlStrCache>
+                <c:ptCount val="1"/>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>4月21日</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>4月20日</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>4月19日</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>4月18日</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>4月17日</c:v>
+                  </c:pt>
+                </c:lvl>
+              </c:multiLvlStrCache>
+            </c:multiLvlStrRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet2!$C$4:$G$4</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>500</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>500</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>550</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>500</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>450</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>"中央値"</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>中央値</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="98b855"/>
+            </a:solidFill>
+            <a:ln w="28440">
+              <a:solidFill>
+                <a:srgbClr val="98b855"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:dLbls>
+            <c:txPr>
+              <a:bodyPr wrap="square"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="Arial"/>
+                  </a:defRPr>
+                </a:pPr>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="r"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:separator>; </c:separator>
+            <c:showLeaderLines val="1"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:multiLvlStrRef>
+              <c:f>Sheet2!$C$2:$G$2</c:f>
+              <c:multiLvlStrCache>
+                <c:ptCount val="1"/>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>4月21日</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>4月20日</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>4月19日</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>4月18日</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>4月17日</c:v>
+                  </c:pt>
+                </c:lvl>
+              </c:multiLvlStrCache>
+            </c:multiLvlStrRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet2!$C$5:$G$5</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>450</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>450</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>750</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>450</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>450</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:hiLowLines>
+          <c:spPr>
+            <a:ln w="0">
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+        </c:hiLowLines>
+        <c:marker val="0"/>
+        <c:axId val="12078986"/>
+        <c:axId val="64069900"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="12078986"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="m\月d\日" sourceLinked="0"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:ln w="9360">
+            <a:solidFill>
+              <a:srgbClr val="878787"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="Calibri"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="64069900"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="64069900"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9360">
+              <a:solidFill>
+                <a:srgbClr val="878787"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="0"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:ln w="9360">
+            <a:solidFill>
+              <a:srgbClr val="878787"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="Calibri"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="12078986"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Calibri"/>
+            </a:defRPr>
+          </a:pPr>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:srgbClr val="ffffff"/>
+    </a:solidFill>
+    <a:ln w="9360">
+      <a:solidFill>
+        <a:srgbClr val="d9d9d9"/>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+  </c:spPr>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart68.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <c:chart>
+    <c:autoTitleDeleted val="1"/>
+    <c:plotArea>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>"標準偏差"</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>標準偏差</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="4a7ebb"/>
+            </a:solidFill>
+            <a:ln w="28440">
+              <a:solidFill>
+                <a:srgbClr val="4a7ebb"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:dLbls>
+            <c:txPr>
+              <a:bodyPr wrap="square"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="Arial"/>
+                  </a:defRPr>
+                </a:pPr>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="r"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:separator>; </c:separator>
+            <c:showLeaderLines val="1"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:multiLvlStrRef>
+              <c:f>Sheet2!$C$16:$G$16</c:f>
+              <c:multiLvlStrCache>
+                <c:ptCount val="1"/>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>4月21日</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>4月20日</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>4月19日</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>4月18日</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>4月17日</c:v>
+                  </c:pt>
+                </c:lvl>
+              </c:multiLvlStrCache>
+            </c:multiLvlStrRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet2!$C$17:$G$17</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>450</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>650</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>450</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>650</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>500</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>"中央値"</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>中央値</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="be4b48"/>
+            </a:solidFill>
+            <a:ln w="28440">
+              <a:solidFill>
+                <a:srgbClr val="be4b48"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:dLbls>
+            <c:txPr>
+              <a:bodyPr wrap="square"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="Arial"/>
+                  </a:defRPr>
+                </a:pPr>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="r"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:separator>; </c:separator>
+            <c:showLeaderLines val="1"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:multiLvlStrRef>
+              <c:f>Sheet2!$C$16:$G$16</c:f>
+              <c:multiLvlStrCache>
+                <c:ptCount val="1"/>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>4月21日</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>4月20日</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>4月19日</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>4月18日</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>4月17日</c:v>
+                  </c:pt>
+                </c:lvl>
+              </c:multiLvlStrCache>
+            </c:multiLvlStrRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet2!$C$18:$G$18</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>450</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>550</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>500</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>550</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>450</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>"分散"</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>分散</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="98b855"/>
+            </a:solidFill>
+            <a:ln w="28440">
+              <a:solidFill>
+                <a:srgbClr val="98b855"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:dLbls>
+            <c:txPr>
+              <a:bodyPr wrap="square"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="Arial"/>
+                  </a:defRPr>
+                </a:pPr>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="r"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:separator>; </c:separator>
+            <c:showLeaderLines val="1"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:multiLvlStrRef>
+              <c:f>Sheet2!$C$16:$G$16</c:f>
+              <c:multiLvlStrCache>
+                <c:ptCount val="1"/>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>4月21日</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>4月20日</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>4月19日</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>4月18日</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>4月17日</c:v>
+                  </c:pt>
+                </c:lvl>
+              </c:multiLvlStrCache>
+            </c:multiLvlStrRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet2!$C$19:$G$19</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>500</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>750</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>450</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>750</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>550</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:hiLowLines>
+          <c:spPr>
+            <a:ln w="0">
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+        </c:hiLowLines>
+        <c:marker val="0"/>
+        <c:axId val="82434566"/>
+        <c:axId val="34630508"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="82434566"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="m\月d\日" sourceLinked="0"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:ln w="9360">
+            <a:solidFill>
+              <a:srgbClr val="878787"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="Calibri"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="34630508"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="34630508"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9360">
+              <a:solidFill>
+                <a:srgbClr val="878787"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="0"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:ln w="9360">
+            <a:solidFill>
+              <a:srgbClr val="878787"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="Calibri"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="82434566"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Calibri"/>
+            </a:defRPr>
+          </a:pPr>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:srgbClr val="ffffff"/>
+    </a:solidFill>
+    <a:ln w="9360">
+      <a:solidFill>
+        <a:srgbClr val="d9d9d9"/>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+  </c:spPr>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart69.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <c:chart>
+    <c:autoTitleDeleted val="1"/>
+    <c:plotArea>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>"最大値"</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>最大値</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="4a7ebb"/>
+            </a:solidFill>
+            <a:ln w="28440">
+              <a:solidFill>
+                <a:srgbClr val="4a7ebb"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:dLbls>
+            <c:txPr>
+              <a:bodyPr wrap="square"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="Arial"/>
+                  </a:defRPr>
+                </a:pPr>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="r"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:separator>; </c:separator>
+            <c:showLeaderLines val="1"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:multiLvlStrRef>
+              <c:f>Sheet2!$C$2:$G$2</c:f>
+              <c:multiLvlStrCache>
+                <c:ptCount val="1"/>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>4月21日</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>4月20日</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>4月19日</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>4月18日</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>4月17日</c:v>
+                  </c:pt>
+                </c:lvl>
+              </c:multiLvlStrCache>
+            </c:multiLvlStrRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet2!$C$3:$G$3</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>450</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>450</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>650</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>450</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>450</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>"最小値"</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>最小値</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="be4b48"/>
+            </a:solidFill>
+            <a:ln w="28440">
+              <a:solidFill>
+                <a:srgbClr val="be4b48"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:dLbls>
+            <c:txPr>
+              <a:bodyPr wrap="square"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="Arial"/>
+                  </a:defRPr>
+                </a:pPr>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="r"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:separator>; </c:separator>
+            <c:showLeaderLines val="1"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:multiLvlStrRef>
+              <c:f>Sheet2!$C$2:$G$2</c:f>
+              <c:multiLvlStrCache>
+                <c:ptCount val="1"/>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>4月21日</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>4月20日</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>4月19日</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>4月18日</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>4月17日</c:v>
+                  </c:pt>
+                </c:lvl>
+              </c:multiLvlStrCache>
+            </c:multiLvlStrRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet2!$C$4:$G$4</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>500</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>500</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>550</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>500</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>450</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>"中央値"</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>中央値</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="98b855"/>
+            </a:solidFill>
+            <a:ln w="28440">
+              <a:solidFill>
+                <a:srgbClr val="98b855"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:dLbls>
+            <c:txPr>
+              <a:bodyPr wrap="square"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="Arial"/>
+                  </a:defRPr>
+                </a:pPr>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="r"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:separator>; </c:separator>
+            <c:showLeaderLines val="1"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:multiLvlStrRef>
+              <c:f>Sheet2!$C$2:$G$2</c:f>
+              <c:multiLvlStrCache>
+                <c:ptCount val="1"/>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>4月21日</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>4月20日</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>4月19日</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>4月18日</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>4月17日</c:v>
+                  </c:pt>
+                </c:lvl>
+              </c:multiLvlStrCache>
+            </c:multiLvlStrRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet2!$C$5:$G$5</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>450</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>450</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>750</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>450</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>450</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:hiLowLines>
+          <c:spPr>
+            <a:ln w="0">
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+        </c:hiLowLines>
+        <c:marker val="0"/>
+        <c:axId val="58173928"/>
+        <c:axId val="16467418"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="58173928"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="m\月d\日" sourceLinked="0"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:ln w="9360">
+            <a:solidFill>
+              <a:srgbClr val="878787"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="Calibri"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="16467418"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="16467418"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9360">
+              <a:solidFill>
+                <a:srgbClr val="878787"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="0"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:ln w="9360">
+            <a:solidFill>
+              <a:srgbClr val="878787"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="Calibri"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="58173928"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Calibri"/>
+            </a:defRPr>
+          </a:pPr>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:srgbClr val="ffffff"/>
+    </a:solidFill>
+    <a:ln w="9360">
+      <a:solidFill>
+        <a:srgbClr val="d9d9d9"/>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+  </c:spPr>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart70.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <c:chart>
+    <c:autoTitleDeleted val="1"/>
+    <c:plotArea>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>"標準偏差"</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>標準偏差</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="4a7ebb"/>
+            </a:solidFill>
+            <a:ln w="28440">
+              <a:solidFill>
+                <a:srgbClr val="4a7ebb"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:dLbls>
+            <c:txPr>
+              <a:bodyPr wrap="square"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="Arial"/>
+                  </a:defRPr>
+                </a:pPr>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="r"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:separator>; </c:separator>
+            <c:showLeaderLines val="1"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:multiLvlStrRef>
+              <c:f>Sheet2!$C$16:$G$16</c:f>
+              <c:multiLvlStrCache>
+                <c:ptCount val="1"/>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>4月21日</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>4月20日</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>4月19日</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>4月18日</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>4月17日</c:v>
+                  </c:pt>
+                </c:lvl>
+              </c:multiLvlStrCache>
+            </c:multiLvlStrRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet2!$C$17:$G$17</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>450</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>650</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>450</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>650</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>500</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>"中央値"</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>中央値</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="be4b48"/>
+            </a:solidFill>
+            <a:ln w="28440">
+              <a:solidFill>
+                <a:srgbClr val="be4b48"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:dLbls>
+            <c:txPr>
+              <a:bodyPr wrap="square"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="Arial"/>
+                  </a:defRPr>
+                </a:pPr>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="r"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:separator>; </c:separator>
+            <c:showLeaderLines val="1"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:multiLvlStrRef>
+              <c:f>Sheet2!$C$16:$G$16</c:f>
+              <c:multiLvlStrCache>
+                <c:ptCount val="1"/>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>4月21日</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>4月20日</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>4月19日</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>4月18日</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>4月17日</c:v>
+                  </c:pt>
+                </c:lvl>
+              </c:multiLvlStrCache>
+            </c:multiLvlStrRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet2!$C$18:$G$18</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>450</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>550</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>500</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>550</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>450</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>"分散"</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>分散</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="98b855"/>
+            </a:solidFill>
+            <a:ln w="28440">
+              <a:solidFill>
+                <a:srgbClr val="98b855"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:dLbls>
+            <c:txPr>
+              <a:bodyPr wrap="square"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="Arial"/>
+                  </a:defRPr>
+                </a:pPr>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="r"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:separator>; </c:separator>
+            <c:showLeaderLines val="1"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:multiLvlStrRef>
+              <c:f>Sheet2!$C$16:$G$16</c:f>
+              <c:multiLvlStrCache>
+                <c:ptCount val="1"/>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>4月21日</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>4月20日</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>4月19日</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>4月18日</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>4月17日</c:v>
+                  </c:pt>
+                </c:lvl>
+              </c:multiLvlStrCache>
+            </c:multiLvlStrRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet2!$C$19:$G$19</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>500</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>750</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>450</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>750</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>550</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:hiLowLines>
+          <c:spPr>
+            <a:ln w="0">
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+        </c:hiLowLines>
+        <c:marker val="0"/>
+        <c:axId val="37218579"/>
+        <c:axId val="98010165"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="37218579"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="m\月d\日" sourceLinked="0"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:ln w="9360">
+            <a:solidFill>
+              <a:srgbClr val="878787"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="Calibri"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="98010165"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="98010165"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9360">
+              <a:solidFill>
+                <a:srgbClr val="878787"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="0"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:ln w="9360">
+            <a:solidFill>
+              <a:srgbClr val="878787"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="Calibri"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="37218579"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Calibri"/>
+            </a:defRPr>
+          </a:pPr>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:srgbClr val="ffffff"/>
+    </a:solidFill>
+    <a:ln w="9360">
+      <a:solidFill>
+        <a:srgbClr val="d9d9d9"/>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+  </c:spPr>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart71.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <c:chart>
+    <c:autoTitleDeleted val="1"/>
+    <c:plotArea>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>"最大値"</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>最大値</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="4a7ebb"/>
+            </a:solidFill>
+            <a:ln w="28440">
+              <a:solidFill>
+                <a:srgbClr val="4a7ebb"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+          </c:spPr>
+          <c:dLbls>
+            <c:txPr>
+              <a:bodyPr wrap="none"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                    <a:latin typeface="Arial"/>
+                  </a:defRPr>
+                </a:pPr>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="r"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:separator> </c:separator>
+            <c:showLeaderLines val="1"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:multiLvlStrRef>
+              <c:f>Sheet2!$C$2:$G$2</c:f>
+              <c:multiLvlStrCache>
+                <c:ptCount val="1"/>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>4月21日</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>4月20日</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>4月19日</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>4月18日</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>4月17日</c:v>
+                  </c:pt>
+                </c:lvl>
+              </c:multiLvlStrCache>
+            </c:multiLvlStrRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet2!$C$3:$G$3</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>450</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>450</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>650</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>450</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>450</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>"最小値"</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>最小値</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="be4b48"/>
+            </a:solidFill>
+            <a:ln w="28440">
+              <a:solidFill>
+                <a:srgbClr val="be4b48"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+          </c:spPr>
+          <c:dLbls>
+            <c:txPr>
+              <a:bodyPr wrap="none"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                    <a:latin typeface="Arial"/>
+                  </a:defRPr>
+                </a:pPr>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="r"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:separator> </c:separator>
+            <c:showLeaderLines val="1"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:multiLvlStrRef>
+              <c:f>Sheet2!$C$2:$G$2</c:f>
+              <c:multiLvlStrCache>
+                <c:ptCount val="1"/>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>4月21日</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>4月20日</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>4月19日</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>4月18日</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>4月17日</c:v>
+                  </c:pt>
+                </c:lvl>
+              </c:multiLvlStrCache>
+            </c:multiLvlStrRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet2!$C$4:$G$4</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>500</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>500</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>550</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>500</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>450</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>"中央値"</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>中央値</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="98b855"/>
+            </a:solidFill>
+            <a:ln w="28440">
+              <a:solidFill>
+                <a:srgbClr val="98b855"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+          </c:spPr>
+          <c:dLbls>
+            <c:txPr>
+              <a:bodyPr wrap="none"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                    <a:latin typeface="Arial"/>
+                  </a:defRPr>
+                </a:pPr>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="r"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:separator> </c:separator>
+            <c:showLeaderLines val="1"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:multiLvlStrRef>
+              <c:f>Sheet2!$C$2:$G$2</c:f>
+              <c:multiLvlStrCache>
+                <c:ptCount val="1"/>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>4月21日</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>4月20日</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>4月19日</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>4月18日</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>4月17日</c:v>
+                  </c:pt>
+                </c:lvl>
+              </c:multiLvlStrCache>
+            </c:multiLvlStrRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet2!$C$5:$G$5</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>450</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>450</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>750</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>450</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>450</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:hiLowLines>
+          <c:spPr>
+            <a:ln w="0">
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+        </c:hiLowLines>
+        <c:marker val="1"/>
+        <c:axId val="85783854"/>
+        <c:axId val="54223607"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="85783854"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="m\月d\日" sourceLinked="0"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:ln w="9360">
+            <a:solidFill>
+              <a:srgbClr val="878787"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="Calibri"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="54223607"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="54223607"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9360">
+              <a:solidFill>
+                <a:srgbClr val="878787"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="0"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:ln w="9360">
+            <a:solidFill>
+              <a:srgbClr val="878787"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="Calibri"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="85783854"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Calibri"/>
+            </a:defRPr>
+          </a:pPr>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:srgbClr val="ffffff"/>
+    </a:solidFill>
+    <a:ln w="9360">
+      <a:solidFill>
+        <a:srgbClr val="d9d9d9"/>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+  </c:spPr>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart72.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <c:chart>
+    <c:autoTitleDeleted val="1"/>
+    <c:plotArea>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>"標準偏差"</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>標準偏差</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="4a7ebb"/>
+            </a:solidFill>
+            <a:ln w="28440">
+              <a:solidFill>
+                <a:srgbClr val="4a7ebb"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+          </c:spPr>
+          <c:dLbls>
+            <c:txPr>
+              <a:bodyPr wrap="none"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                    <a:latin typeface="Arial"/>
+                  </a:defRPr>
+                </a:pPr>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="r"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:separator> </c:separator>
+            <c:showLeaderLines val="1"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:multiLvlStrRef>
+              <c:f>Sheet2!$C$16:$G$16</c:f>
+              <c:multiLvlStrCache>
+                <c:ptCount val="1"/>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>4月21日</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>4月20日</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>4月19日</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>4月18日</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>4月17日</c:v>
+                  </c:pt>
+                </c:lvl>
+              </c:multiLvlStrCache>
+            </c:multiLvlStrRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet2!$C$17:$G$17</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>450</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>650</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>450</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>650</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>500</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>"中央値"</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>中央値</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="be4b48"/>
+            </a:solidFill>
+            <a:ln w="28440">
+              <a:solidFill>
+                <a:srgbClr val="be4b48"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+          </c:spPr>
+          <c:dLbls>
+            <c:txPr>
+              <a:bodyPr wrap="none"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                    <a:latin typeface="Arial"/>
+                  </a:defRPr>
+                </a:pPr>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="r"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:separator> </c:separator>
+            <c:showLeaderLines val="1"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:multiLvlStrRef>
+              <c:f>Sheet2!$C$16:$G$16</c:f>
+              <c:multiLvlStrCache>
+                <c:ptCount val="1"/>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>4月21日</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>4月20日</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>4月19日</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>4月18日</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>4月17日</c:v>
+                  </c:pt>
+                </c:lvl>
+              </c:multiLvlStrCache>
+            </c:multiLvlStrRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet2!$C$18:$G$18</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>450</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>550</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>500</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>550</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>450</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>"分散"</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>分散</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="98b855"/>
+            </a:solidFill>
+            <a:ln w="28440">
+              <a:solidFill>
+                <a:srgbClr val="98b855"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+          </c:spPr>
+          <c:dLbls>
+            <c:txPr>
+              <a:bodyPr wrap="none"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                    <a:latin typeface="Arial"/>
+                  </a:defRPr>
+                </a:pPr>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="r"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:separator> </c:separator>
+            <c:showLeaderLines val="1"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:multiLvlStrRef>
+              <c:f>Sheet2!$C$16:$G$16</c:f>
+              <c:multiLvlStrCache>
+                <c:ptCount val="1"/>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>4月21日</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>4月20日</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>4月19日</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>4月18日</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>4月17日</c:v>
+                  </c:pt>
+                </c:lvl>
+              </c:multiLvlStrCache>
+            </c:multiLvlStrRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet2!$C$19:$G$19</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>500</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>750</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>450</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>750</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>550</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:hiLowLines>
+          <c:spPr>
+            <a:ln w="0">
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+        </c:hiLowLines>
+        <c:marker val="1"/>
+        <c:axId val="53498142"/>
+        <c:axId val="97914717"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="53498142"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="m\月d\日" sourceLinked="0"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:ln w="9360">
+            <a:solidFill>
+              <a:srgbClr val="878787"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="Calibri"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="97914717"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="97914717"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9360">
+              <a:solidFill>
+                <a:srgbClr val="878787"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="0"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:ln w="9360">
+            <a:solidFill>
+              <a:srgbClr val="878787"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="Calibri"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="53498142"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Calibri"/>
+            </a:defRPr>
+          </a:pPr>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:srgbClr val="ffffff"/>
+    </a:solidFill>
+    <a:ln w="9360">
+      <a:solidFill>
+        <a:srgbClr val="d9d9d9"/>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+  </c:spPr>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart73.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <c:chart>
+    <c:autoTitleDeleted val="1"/>
+    <c:plotArea>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>"最大値"</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>最大値</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="4a7ebb"/>
+            </a:solidFill>
+            <a:ln w="28440">
+              <a:solidFill>
+                <a:srgbClr val="4a7ebb"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+          </c:spPr>
+          <c:dLbls>
+            <c:txPr>
+              <a:bodyPr wrap="none"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                    <a:latin typeface="Arial"/>
+                  </a:defRPr>
+                </a:pPr>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="r"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:separator> </c:separator>
+            <c:showLeaderLines val="1"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:multiLvlStrRef>
+              <c:f>Sheet3!$C$2:$G$2</c:f>
+              <c:multiLvlStrCache>
+                <c:ptCount val="1"/>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>4月26日</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>4月25日</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>4月24日</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>4月23日</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>4月22日</c:v>
+                  </c:pt>
+                </c:lvl>
+              </c:multiLvlStrCache>
+            </c:multiLvlStrRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet3!$C$3:$G$3</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>650</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>650</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>650</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>450</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>450</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>"最小値"</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>最小値</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="be4b48"/>
+            </a:solidFill>
+            <a:ln w="28440">
+              <a:solidFill>
+                <a:srgbClr val="be4b48"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+          </c:spPr>
+          <c:dLbls>
+            <c:txPr>
+              <a:bodyPr wrap="none"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                    <a:latin typeface="Arial"/>
+                  </a:defRPr>
+                </a:pPr>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="r"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:separator> </c:separator>
+            <c:showLeaderLines val="1"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:multiLvlStrRef>
+              <c:f>Sheet3!$C$2:$G$2</c:f>
+              <c:multiLvlStrCache>
+                <c:ptCount val="1"/>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>4月26日</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>4月25日</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>4月24日</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>4月23日</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>4月22日</c:v>
+                  </c:pt>
+                </c:lvl>
+              </c:multiLvlStrCache>
+            </c:multiLvlStrRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet2!$C$4:$G$4</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>500</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>500</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>550</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>500</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>450</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>"中央値"</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>中央値</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="98b855"/>
+            </a:solidFill>
+            <a:ln w="28440">
+              <a:solidFill>
+                <a:srgbClr val="98b855"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+          </c:spPr>
+          <c:dLbls>
+            <c:txPr>
+              <a:bodyPr wrap="none"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                    <a:latin typeface="Arial"/>
+                  </a:defRPr>
+                </a:pPr>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="r"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:separator> </c:separator>
+            <c:showLeaderLines val="1"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:multiLvlStrRef>
+              <c:f>Sheet3!$C$2:$G$2</c:f>
+              <c:multiLvlStrCache>
+                <c:ptCount val="1"/>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>4月26日</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>4月25日</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>4月24日</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>4月23日</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>4月22日</c:v>
+                  </c:pt>
+                </c:lvl>
+              </c:multiLvlStrCache>
+            </c:multiLvlStrRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet2!$C$5:$G$5</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>450</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>450</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>750</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>450</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>450</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:hiLowLines>
+          <c:spPr>
+            <a:ln w="0">
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+        </c:hiLowLines>
+        <c:marker val="1"/>
+        <c:axId val="61639507"/>
+        <c:axId val="36951278"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="61639507"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="m\月d\日" sourceLinked="0"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:ln w="9360">
+            <a:solidFill>
+              <a:srgbClr val="878787"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="Calibri"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="36951278"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="36951278"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9360">
+              <a:solidFill>
+                <a:srgbClr val="878787"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="0"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:ln w="9360">
+            <a:solidFill>
+              <a:srgbClr val="878787"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="Calibri"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="61639507"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Calibri"/>
+            </a:defRPr>
+          </a:pPr>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:srgbClr val="ffffff"/>
+    </a:solidFill>
+    <a:ln w="9360">
+      <a:solidFill>
+        <a:srgbClr val="d9d9d9"/>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+  </c:spPr>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart74.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <c:chart>
+    <c:autoTitleDeleted val="1"/>
+    <c:plotArea>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>"標準偏差"</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>標準偏差</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="4a7ebb"/>
+            </a:solidFill>
+            <a:ln w="28440">
+              <a:solidFill>
+                <a:srgbClr val="4a7ebb"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+          </c:spPr>
+          <c:dLbls>
+            <c:txPr>
+              <a:bodyPr wrap="none"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                    <a:latin typeface="Arial"/>
+                  </a:defRPr>
+                </a:pPr>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="r"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:separator> </c:separator>
+            <c:showLeaderLines val="1"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:multiLvlStrRef>
+              <c:f>Sheet2!$C$16:$G$16</c:f>
+              <c:multiLvlStrCache>
+                <c:ptCount val="1"/>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>4月21日</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>4月20日</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>4月19日</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>4月18日</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>4月17日</c:v>
+                  </c:pt>
+                </c:lvl>
+              </c:multiLvlStrCache>
+            </c:multiLvlStrRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet2!$C$17:$G$17</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>450</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>650</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>450</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>650</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>500</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>"中央値"</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>中央値</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="be4b48"/>
+            </a:solidFill>
+            <a:ln w="28440">
+              <a:solidFill>
+                <a:srgbClr val="be4b48"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+          </c:spPr>
+          <c:dLbls>
+            <c:txPr>
+              <a:bodyPr wrap="none"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                    <a:latin typeface="Arial"/>
+                  </a:defRPr>
+                </a:pPr>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="r"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:separator> </c:separator>
+            <c:showLeaderLines val="1"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:multiLvlStrRef>
+              <c:f>Sheet2!$C$16:$G$16</c:f>
+              <c:multiLvlStrCache>
+                <c:ptCount val="1"/>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>4月21日</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>4月20日</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>4月19日</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>4月18日</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>4月17日</c:v>
+                  </c:pt>
+                </c:lvl>
+              </c:multiLvlStrCache>
+            </c:multiLvlStrRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet2!$C$18:$G$18</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>450</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>550</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>500</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>550</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>450</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>"分散"</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>分散</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="98b855"/>
+            </a:solidFill>
+            <a:ln w="28440">
+              <a:solidFill>
+                <a:srgbClr val="98b855"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+          </c:spPr>
+          <c:dLbls>
+            <c:txPr>
+              <a:bodyPr wrap="none"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                    <a:latin typeface="Arial"/>
+                  </a:defRPr>
+                </a:pPr>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="r"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:separator> </c:separator>
+            <c:showLeaderLines val="1"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:multiLvlStrRef>
+              <c:f>Sheet2!$C$16:$G$16</c:f>
+              <c:multiLvlStrCache>
+                <c:ptCount val="1"/>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>4月21日</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>4月20日</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>4月19日</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>4月18日</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>4月17日</c:v>
+                  </c:pt>
+                </c:lvl>
+              </c:multiLvlStrCache>
+            </c:multiLvlStrRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet2!$C$19:$G$19</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>500</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>750</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>450</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>750</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>550</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:hiLowLines>
+          <c:spPr>
+            <a:ln w="0">
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+        </c:hiLowLines>
+        <c:marker val="1"/>
+        <c:axId val="33367644"/>
+        <c:axId val="2260802"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="33367644"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="m\月d\日" sourceLinked="0"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:ln w="9360">
+            <a:solidFill>
+              <a:srgbClr val="878787"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="Calibri"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="2260802"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="2260802"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9360">
+              <a:solidFill>
+                <a:srgbClr val="878787"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="0"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:ln w="9360">
+            <a:solidFill>
+              <a:srgbClr val="878787"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="Calibri"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="33367644"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Calibri"/>
+            </a:defRPr>
+          </a:pPr>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:srgbClr val="ffffff"/>
+    </a:solidFill>
+    <a:ln w="9360">
+      <a:solidFill>
+        <a:srgbClr val="d9d9d9"/>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+  </c:spPr>
+</c:chartSpace>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <xdr:twoCellAnchor editAs="oneCell">
@@ -2084,9 +7043,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>18</xdr:col>
-      <xdr:colOff>632520</xdr:colOff>
+      <xdr:colOff>632160</xdr:colOff>
       <xdr:row>13</xdr:row>
-      <xdr:rowOff>127080</xdr:rowOff>
+      <xdr:rowOff>126720</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -2094,8 +7053,8 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="11535120" y="57600"/>
-        <a:ext cx="3864960" cy="2219040"/>
+        <a:off x="11553120" y="57600"/>
+        <a:ext cx="3869640" cy="2218680"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -2114,9 +7073,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>18</xdr:col>
-      <xdr:colOff>701640</xdr:colOff>
+      <xdr:colOff>701280</xdr:colOff>
       <xdr:row>29</xdr:row>
-      <xdr:rowOff>131400</xdr:rowOff>
+      <xdr:rowOff>131040</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -2124,8 +7083,8 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="11515320" y="2458800"/>
-        <a:ext cx="3953880" cy="2459160"/>
+        <a:off x="11533320" y="2458800"/>
+        <a:ext cx="3958560" cy="2458800"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -2149,9 +7108,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>18</xdr:col>
-      <xdr:colOff>584640</xdr:colOff>
+      <xdr:colOff>584280</xdr:colOff>
       <xdr:row>13</xdr:row>
-      <xdr:rowOff>57600</xdr:rowOff>
+      <xdr:rowOff>57240</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -2159,8 +7118,8 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="11485800" y="31680"/>
-        <a:ext cx="3866400" cy="2175480"/>
+        <a:off x="11503800" y="31680"/>
+        <a:ext cx="3871080" cy="2175120"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -2179,9 +7138,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>18</xdr:col>
-      <xdr:colOff>675720</xdr:colOff>
+      <xdr:colOff>675360</xdr:colOff>
       <xdr:row>28</xdr:row>
-      <xdr:rowOff>134280</xdr:rowOff>
+      <xdr:rowOff>133920</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -2189,12 +7148,317 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="11515320" y="2549160"/>
-        <a:ext cx="3927960" cy="2209320"/>
+        <a:off x="11533320" y="2549160"/>
+        <a:ext cx="3932640" cy="2208960"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>31680</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>583200</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>56160</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame>
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="4" name="Chart 3"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="11548080" y="31680"/>
+        <a:ext cx="3882600" cy="2158200"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>29520</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>74520</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>674280</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>132840</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame>
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="5" name="Chart 4"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="11577600" y="2531880"/>
+        <a:ext cx="3944160" cy="2192040"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>210240</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>25200</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame>
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="6" name="Chart 5"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="6598800" y="162000"/>
+        <a:ext cx="4334760" cy="2158560"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>210240</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>24840</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame>
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="7" name="Chart 6"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="6598800" y="2457360"/>
+        <a:ext cx="4334760" cy="2158560"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>207360</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>25560</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame>
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="8" name="Chart 7"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="6598800" y="162000"/>
+        <a:ext cx="4331880" cy="2158920"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId5"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>207360</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>25200</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame>
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="9" name="Chart 8"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="6598800" y="2457360"/>
+        <a:ext cx="4331880" cy="2158920"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId6"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>201240</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>25920</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame>
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="10" name="Chart 1"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="6598800" y="162000"/>
+        <a:ext cx="4325760" cy="2159280"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId7"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>201240</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>25560</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame>
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="11" name="Chart 2"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="6598800" y="2457360"/>
+        <a:ext cx="4325760" cy="2159280"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId8"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>201240</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>25920</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame>
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="12" name="Chart 9"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="6598800" y="162000"/>
+        <a:ext cx="4325760" cy="2159280"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId9"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>201240</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>25560</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame>
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="13" name="Chart 10"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="6598800" y="2457360"/>
+        <a:ext cx="4325760" cy="2159280"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId10"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2209,7 +7473,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A2:G19"/>
-  <sheetFormatPr defaultColWidth="11.640625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.66015625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="2" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C2" s="1" t="n">
@@ -2398,7 +7662,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A2:G19"/>
-  <sheetFormatPr defaultColWidth="11.640625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.66015625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="2" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C2" s="1" t="n">
@@ -2566,6 +7830,195 @@
         <v>750</v>
       </c>
       <c r="G19" s="3" t="n">
+        <v>550</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,標準"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,標準"&amp;12ページ &amp;P</oddFooter>
+  </headerFooter>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A2:G19"/>
+  <sheetFormatPr defaultColWidth="11.70703125" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetData>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C2" s="4" t="n">
+        <v>45038</v>
+      </c>
+      <c r="D2" s="4" t="n">
+        <f aca="false">C2+1</f>
+        <v>45039</v>
+      </c>
+      <c r="E2" s="4" t="n">
+        <f aca="false">D2+1</f>
+        <v>45040</v>
+      </c>
+      <c r="F2" s="4" t="n">
+        <f aca="false">E2+1</f>
+        <v>45041</v>
+      </c>
+      <c r="G2" s="4" t="n">
+        <f aca="false">F2+1</f>
+        <v>45042</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B3" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="C3" s="5" t="n">
+        <v>650</v>
+      </c>
+      <c r="D3" s="5" t="n">
+        <v>650</v>
+      </c>
+      <c r="E3" s="5" t="n">
+        <v>650</v>
+      </c>
+      <c r="F3" s="5" t="n">
+        <v>450</v>
+      </c>
+      <c r="G3" s="5" t="n">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B4" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C4" s="5" t="n">
+        <v>550</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>550</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>550</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>500</v>
+      </c>
+      <c r="G4" s="5" t="n">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="5"/>
+      <c r="B5" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>650</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>650</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>750</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>450</v>
+      </c>
+      <c r="G5" s="5" t="n">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="5"/>
+      <c r="B6" s="5"/>
+      <c r="C6" s="5"/>
+      <c r="D6" s="5"/>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C16" s="4" t="n">
+        <v>45038</v>
+      </c>
+      <c r="D16" s="4" t="n">
+        <f aca="false">C16+1</f>
+        <v>45039</v>
+      </c>
+      <c r="E16" s="4" t="n">
+        <f aca="false">D16+1</f>
+        <v>45040</v>
+      </c>
+      <c r="F16" s="4" t="n">
+        <f aca="false">E16+1</f>
+        <v>45041</v>
+      </c>
+      <c r="G16" s="4" t="n">
+        <f aca="false">F16+1</f>
+        <v>45042</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B17" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>650</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>650</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>450</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>650</v>
+      </c>
+      <c r="G17" s="5" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B18" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>550</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>550</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>500</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>550</v>
+      </c>
+      <c r="G18" s="5" t="n">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B19" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="C19" s="5" t="n">
+        <v>750</v>
+      </c>
+      <c r="D19" s="5" t="n">
+        <v>750</v>
+      </c>
+      <c r="E19" s="5" t="n">
+        <v>450</v>
+      </c>
+      <c r="F19" s="5" t="n">
+        <v>750</v>
+      </c>
+      <c r="G19" s="5" t="n">
         <v>550</v>
       </c>
     </row>
